--- a/data/trans_bre/P38C-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P38C-Edad-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 15,87</t>
+          <t>2,09; 16,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 23,23</t>
+          <t>0,96; 23,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 30,03</t>
+          <t>3,75; 30,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 55,7</t>
+          <t>1,77; 60,31</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,3; 18,92</t>
+          <t>8,15; 18,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 13,65</t>
+          <t>-22,77; 13,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,56; 29,59</t>
+          <t>11,35; 28,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,91; 21,46</t>
+          <t>-35,72; 20,84</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 8,24</t>
+          <t>0,19; 8,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 11,83</t>
+          <t>2,55; 12,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 10,49</t>
+          <t>0,22; 11,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 16,01</t>
+          <t>3,18; 16,35</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 6,81</t>
+          <t>-0,67; 6,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 64,71</t>
+          <t>3,56; 61,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 8,08</t>
+          <t>-0,76; 8,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 249,49</t>
+          <t>4,1; 208,37</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 4,36</t>
+          <t>-2,75; 4,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 4,87</t>
+          <t>-1,06; 4,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 4,82</t>
+          <t>-2,92; 5,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 5,36</t>
+          <t>-1,13; 5,09</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 3,52</t>
+          <t>-1,22; 3,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,61</t>
+          <t>0,93; 5,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 3,7</t>
+          <t>-1,24; 3,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,99</t>
+          <t>0,98; 6,04</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 3,15</t>
+          <t>-1,72; 3,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; -0,06</t>
+          <t>-3,59; -0,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 3,28</t>
+          <t>-1,75; 3,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,69; -0,06</t>
+          <t>-3,64; -0,08</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,26; 7,79</t>
+          <t>4,23; 7,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,76; 28,75</t>
+          <t>4,53; 30,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,19; 9,64</t>
+          <t>5,08; 9,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,03; 51,8</t>
+          <t>5,62; 52,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P38C-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P38C-Edad-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12,45</t>
+          <t>14,74</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 16,12</t>
+          <t>2,49; 15,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 23,89</t>
+          <t>3,91; 25,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 30,82</t>
+          <t>4,44; 30,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 60,31</t>
+          <t>7,48; 67,2</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>11,18</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,15; 18,53</t>
+          <t>8,94; 18,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 13,34</t>
+          <t>4,37; 18,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,35; 28,03</t>
+          <t>12,57; 28,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,72; 20,84</t>
+          <t>6,26; 30,46</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,22</t>
+          <t>9,18</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 8,75</t>
+          <t>0,08; 8,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 12,15</t>
+          <t>4,54; 13,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 11,22</t>
+          <t>0,11; 10,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 16,35</t>
+          <t>5,8; 18,71</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>28,6</t>
+          <t>4,2</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 6,97</t>
+          <t>-0,79; 6,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 61,91</t>
+          <t>1,05; 7,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 8,17</t>
+          <t>-0,86; 7,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,1; 208,37</t>
+          <t>1,2; 8,85</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,88</t>
+          <t>3,15</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 4,57</t>
+          <t>-2,95; 4,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 4,6</t>
+          <t>0,35; 5,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 5,07</t>
+          <t>-3,15; 4,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 5,09</t>
+          <t>0,42; 6,5</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>2,05</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,23</t>
+          <t>-1,3; 3,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,63</t>
+          <t>-0,06; 4,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 3,38</t>
+          <t>-1,32; 3,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,98; 6,04</t>
+          <t>-0,07; 4,8</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-1,84</t>
+          <t>-1,69</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,87%</t>
+          <t>-1,72%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 3,1</t>
+          <t>-1,64; 3,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,59; -0,08</t>
+          <t>-3,43; 0,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,22</t>
+          <t>-1,66; 3,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,64; -0,08</t>
+          <t>-3,48; 0,69</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11,63</t>
+          <t>7,19</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,57</t>
+          <t>4,13; 7,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,53; 30,02</t>
+          <t>5,14; 9,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,08; 9,42</t>
+          <t>4,96; 9,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,62; 52,69</t>
+          <t>6,35; 12,02</t>
         </is>
       </c>
     </row>
